--- a/data/trans_orig/P21D_6_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P21D_6_R-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención fisioterapéutica, no la pudo recibir por motivos económicos en 2023</t>
+          <t>Población que, necesitando atención fisioterapéutica, no la pudo recibir por motivos económicos en 2023 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,97 +730,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>515</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1776</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>515</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2082</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3343</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>515</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2766</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>223163</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>224939</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>215870</t>
+          <t>214851</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>440125</t>
+          <t>439548</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4673</t>
+          <t>4735</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2541</t>
+          <t>2498</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>493</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5748</t>
+          <t>5579</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>176991</t>
+          <t>176929</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>175495</t>
+          <t>175538</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>353951</t>
+          <t>354120</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>359180</t>
+          <t>359206</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>7205</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,62 +1451,62 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1165</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>5966</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1004</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>6024</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -1524,17 +1524,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>414192</t>
+          <t>414191</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>409958</t>
+          <t>407990</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>415196</t>
+          <t>415195</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>77787</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78952</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>488123</t>
+          <t>488181</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>415196</t>
+          <t>415195</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>415196</t>
+          <t>415195</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>415196</t>
+          <t>415195</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>1158</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12107</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>3042</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10717</t>
+          <t>10934</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6212</t>
+          <t>5437</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18431</t>
+          <t>17734</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>443122</t>
+          <t>443181</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>454167</t>
+          <t>454071</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>328040</t>
+          <t>327823</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>335870</t>
+          <t>335715</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>775554</t>
+          <t>776251</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>787773</t>
+          <t>788548</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7507</t>
+          <t>6925</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4135</t>
+          <t>4640</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15152</t>
+          <t>15117</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4883</t>
+          <t>5521</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16617</t>
+          <t>17399</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>213564</t>
+          <t>214146</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>400704</t>
+          <t>400739</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>411721</t>
+          <t>411216</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>620310</t>
+          <t>619528</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>632044</t>
+          <t>631406</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4140</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>589</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5387</t>
+          <t>6026</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>590</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5777</t>
+          <t>5791</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>119187</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>123327</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>313369</t>
+          <t>312730</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>318168</t>
+          <t>318167</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>436307</t>
+          <t>436293</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>441493</t>
+          <t>441494</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3734</t>
+          <t>3267</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17363</t>
+          <t>17559</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12203</t>
+          <t>12654</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25981</t>
+          <t>26341</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17883</t>
+          <t>18139</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>37681</t>
+          <t>37511</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1604062</t>
+          <t>1603866</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1617691</t>
+          <t>1618158</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1522328</t>
+          <t>1521968</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1536106</t>
+          <t>1535655</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3132053</t>
+          <t>3132223</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3151851</t>
+          <t>3151595</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,43%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21D_6_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P21D_6_R-Clase-trans_orig.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>510</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3101</t>
+          <t>2767</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>510</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3343</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>224939</t>
+          <t>244410</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -873,27 +873,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>217437</t>
+          <t>234314</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>214851</t>
+          <t>232057</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>217952</t>
+          <t>234824</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -908,27 +908,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>442376</t>
+          <t>478724</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>439548</t>
+          <t>476150</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>442891</t>
+          <t>479234</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>99,89%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>224939</t>
+          <t>244410</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>224939</t>
+          <t>244410</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>224939</t>
+          <t>244410</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>217952</t>
+          <t>234824</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>217952</t>
+          <t>234824</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>217952</t>
+          <t>234824</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>442891</t>
+          <t>479234</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>442891</t>
+          <t>479234</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>442891</t>
+          <t>479234</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1447</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4735</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>525</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1113,12 +1113,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2498</t>
+          <t>2924</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>523</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5579</t>
+          <t>5602</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -1181,27 +1181,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>180217</t>
+          <t>195416</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>176929</t>
+          <t>192037</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>181664</t>
+          <t>196927</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1216,27 +1216,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>177540</t>
+          <t>196097</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>175538</t>
+          <t>193698</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>178036</t>
+          <t>196622</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>357756</t>
+          <t>391512</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>354120</t>
+          <t>387947</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>359206</t>
+          <t>393026</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,87%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>181664</t>
+          <t>196927</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>181664</t>
+          <t>196927</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>181664</t>
+          <t>196927</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>178036</t>
+          <t>196622</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>178036</t>
+          <t>196622</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>178036</t>
+          <t>196622</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>359699</t>
+          <t>393549</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>359699</t>
+          <t>393549</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>359699</t>
+          <t>393549</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>995</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7205</t>
+          <t>4983</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>995</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1491,12 +1491,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5966</t>
+          <t>4985</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -1524,27 +1524,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>414191</t>
+          <t>187842</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>407990</t>
+          <t>183854</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>415195</t>
+          <t>188837</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>78952</t>
+          <t>86621</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1594,27 +1594,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>493143</t>
+          <t>274463</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>488181</t>
+          <t>270473</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>494147</t>
+          <t>275458</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>415195</t>
+          <t>188837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>415195</t>
+          <t>188837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>415195</t>
+          <t>188837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>78952</t>
+          <t>86621</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>78952</t>
+          <t>86621</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>78952</t>
+          <t>86621</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>494147</t>
+          <t>275458</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>494147</t>
+          <t>275458</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>494147</t>
+          <t>275458</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4837</t>
+          <t>4857</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>12815</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5964</t>
+          <t>6518</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>3287</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10934</t>
+          <t>11758</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>10801</t>
+          <t>11375</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5437</t>
+          <t>6003</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17734</t>
+          <t>18480</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>450392</t>
+          <t>505975</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>443181</t>
+          <t>498017</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>454071</t>
+          <t>509001</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>332793</t>
+          <t>380148</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>327823</t>
+          <t>374908</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>335715</t>
+          <t>383379</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>783184</t>
+          <t>886123</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>776251</t>
+          <t>879018</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>788548</t>
+          <t>891495</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>455229</t>
+          <t>510832</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>455229</t>
+          <t>510832</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>455229</t>
+          <t>510832</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>338757</t>
+          <t>386666</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>338757</t>
+          <t>386666</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>338757</t>
+          <t>386666</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>793985</t>
+          <t>897498</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>793985</t>
+          <t>897498</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>793985</t>
+          <t>897498</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6925</t>
+          <t>7388</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8948</t>
+          <t>9278</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4640</t>
+          <t>5150</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15117</t>
+          <t>15276</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>10257</t>
+          <t>10546</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5521</t>
+          <t>5881</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17399</t>
+          <t>16983</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -2210,27 +2210,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>219762</t>
+          <t>263736</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>214146</t>
+          <t>257616</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>221071</t>
+          <t>265004</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>406908</t>
+          <t>378603</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>400739</t>
+          <t>372605</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>411216</t>
+          <t>382731</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>626670</t>
+          <t>642339</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>619528</t>
+          <t>635902</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>631406</t>
+          <t>647004</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>221071</t>
+          <t>265004</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>221071</t>
+          <t>265004</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>221071</t>
+          <t>265004</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>415856</t>
+          <t>387881</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>415856</t>
+          <t>387881</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>415856</t>
+          <t>387881</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>636927</t>
+          <t>652885</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>636927</t>
+          <t>652885</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>636927</t>
+          <t>652885</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2339</t>
+          <t>2424</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>618</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6026</t>
+          <t>6168</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,22 +2510,22 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2339</t>
+          <t>2424</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>602</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5791</t>
+          <t>6405</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>123327</t>
+          <t>117437</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>316417</t>
+          <t>352799</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>312730</t>
+          <t>349055</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>318167</t>
+          <t>354605</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,27 +2623,27 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>439745</t>
+          <t>470236</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>436293</t>
+          <t>466255</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>441494</t>
+          <t>472058</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>123327</t>
+          <t>117437</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>123327</t>
+          <t>117437</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>123327</t>
+          <t>117437</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>318756</t>
+          <t>355223</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>318756</t>
+          <t>355223</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>318756</t>
+          <t>355223</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>442084</t>
+          <t>472660</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>442084</t>
+          <t>472660</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>442084</t>
+          <t>472660</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,27 +2783,27 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>8597</t>
+          <t>8631</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3267</t>
+          <t>3767</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17559</t>
+          <t>16492</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>18261</t>
+          <t>19255</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12654</t>
+          <t>13315</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26341</t>
+          <t>27506</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>26859</t>
+          <t>27887</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18139</t>
+          <t>19708</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>37511</t>
+          <t>39259</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -2896,22 +2896,22 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1612828</t>
+          <t>1514817</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1603866</t>
+          <t>1506956</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1618158</t>
+          <t>1519681</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1530048</t>
+          <t>1628582</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1521968</t>
+          <t>1620331</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1535655</t>
+          <t>1634522</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>3142875</t>
+          <t>3143397</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3132223</t>
+          <t>3132025</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3151595</t>
+          <t>3151576</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1621425</t>
+          <t>1523448</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1621425</t>
+          <t>1523448</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1621425</t>
+          <t>1523448</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1548309</t>
+          <t>1647837</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1548309</t>
+          <t>1647837</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1548309</t>
+          <t>1647837</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>3169734</t>
+          <t>3171284</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3169734</t>
+          <t>3171284</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3169734</t>
+          <t>3171284</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
